--- a/MajFDS/Datas/FdsExcelNoAPI.xlsx
+++ b/MajFDS/Datas/FdsExcelNoAPI.xlsx
@@ -17,6 +17,7 @@
     <sheet name="WS D80-FR" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="ACETATE DE BUTYLE-FR" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="DIACETONE ALCOOL" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="FDS WHITE SPIRIT-FR" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -657,7 +658,6 @@
           <t>Numéro ONU ADR</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -809,6 +809,223 @@
       <c r="A60" t="inlineStr">
         <is>
           <t>Mentions complémentaires</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>FDS WHITE SPIRIT-FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Pictogrammes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GHS02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Inflammable</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GHS07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nocif / Irritant</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GHS08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Danger grave pour la santé</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Contient</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hydrocarbons, C9-C11, n-alkanes, isoalkanes, cyclics, 2 aromatics</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Numéro ONU ADR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UN3295</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mention d'avertissement</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Danger</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mentions de danger</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>H226</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Liquide et vapeurs inflammables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>H336</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Peut provoquer somnolence ou vertiges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>H304</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Peut être mortel en cas d'ingestion et de pénétration dans les voies respiratoires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Conseils de prudence</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>En cas de consultation d'un médecin, garder à disposition le récipient ou l'étiquette.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P102</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tenir hors de portée des enfants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P210</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tenir à l'écart de la chaleur, des surfaces chaudes, des étincelles, des flammes nues et de toute autre source d'inflammation. Ne pas fumer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P261</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Éviter de respirer les poussières/fumées/gaz/ brouillards/vapeurs/ aérosols.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Mentions complémentaires</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EUH066</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>L'exposition répétée peut provoquer dessèchement ou gerçures de la peau.</t>
         </is>
       </c>
     </row>

--- a/MajFDS/Datas/FdsExcelNoAPI.xlsx
+++ b/MajFDS/Datas/FdsExcelNoAPI.xlsx
@@ -18,6 +18,8 @@
     <sheet name="ACETATE DE BUTYLE-FR" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="DIACETONE ALCOOL" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="FDS WHITE SPIRIT-FR" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="FDS ACETATE D_ETHYLE-FR" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="FDS DILUANT CELLULOSIQUE-FR" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1034,6 +1036,735 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>FDS ACETATE D_ETHYLE-FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Pictogrammes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GHS02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Inflammable</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GHS07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nocif / Irritant</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Contient</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Numéro ONU ADR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UN1173</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mention d'avertissement</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Danger</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mentions de danger</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>H225</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Liquide et vapeurs très inflammables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>H319</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Provoque une sévère irritation des yeux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>H336</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Peut provoquer somnolence ou vertiges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Conseils de prudence</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P243</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Prendre des mesures de précaution contre les décharges électrostatiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P303+P361+P353</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EN CAS DE CONTACT AVEC LA PEAU (ou les cheveux): Enlever immédiatement tous les vêtements contaminés. Rincer la peau à l'eau [ou se doucher].</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P304+P340</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>EN CAS D'INHALATION: transporter la personne à l'extérieur et la maintenir dans une position où elle peut confortablement respirer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P305+P351+P338</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>EN CAS DE CONTACT AVEC LES YEUX: Rincer avec précaution à l'eau pendant plusieurs minutes. Enlever les lentilles de contact si la victime en porte et si elles peuvent être facilement enlevées. Continuer à rincer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P337+P313</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Si l'irritation oculaire persiste: consulter un médecin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P403+P233</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Stocker dans un endroit bien ventilé. Maintenir le récipient fermé de manière étanche.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P501</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Éliminer le contenu/récipient dans …</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Mentions complémentaires</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EUH066</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>L'exposition répétée peut provoquer dessèchement ou gerçures de la peau.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>FDS DILUANT CELLULOSIQUE-FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Pictogrammes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GHS02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Inflammable</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GHS07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nocif / Irritant</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GHS08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Danger grave pour la santé</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Contient</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>toluène</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Numéro ONU ADR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UN1263</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mention d'avertissement</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Danger</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mentions de danger</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>H225</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Liquide et vapeurs très inflammables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>H315</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Provoque une irritation cutanée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>H319</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Provoque une sévère irritation des yeux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>H336</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Peut provoquer somnolence ou vertiges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>H361</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Susceptible de nuire à la fertilité ou au foetus &lt;indiquer l'effet s'il est connu&gt; &lt;indiquer la voie d'exposition s'il est formellement prouvé qu'aucune autre voie d'exposition ne conduit au même danger&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>H373</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Risque présumé d'effets graves pour les organes &lt;ou indiquer tous les organes affectés, s'ils sont connus&gt; à la suite d'expositions répétées ou d'une exposition prolongée &lt;indiquer la voie d'exposition s'il est formellement prouvé qu'aucune autre voie d'exposition ne conduit au même danger&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Conseils de prudence</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P201</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Se procurer les instructions spéciales avant utilisation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P202</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ne pas manipuler avant d'avoir lu et compris toutes les précautions de sécurité.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P210</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tenir à l'écart de la chaleur, des surfaces chaudes, des étincelles, des flammes nues et de toute autre source d'inflammation. Ne pas fumer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P233</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Maintenir le récipient fermé de manière étanche.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P240</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Mise à la terre et liaison équipotentielle du récipient et du matériel de réception</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P241</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Utiliser du matériel [électrique/de ventilation/ d'éclairage/…] antidéflagrant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P260</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ne pas respirer les poussières/fumées/gaz/brouillards/vapeurs/ aérosols.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P264</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Se laver … soigneusement après manipulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P271</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Utiliser seulement en plein air ou dans un endroit bien ventilé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P280</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Porter des gants de protection/des vêtements de protection/un équipement de protection des yeux/du visage/une protection auditive/ …</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>P302+P352</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>EN CAS DE CONTACT AVEC LA PEAU: Laver abondamment à l'eau/…</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P303+P361+P353</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>EN CAS DE CONTACT AVEC LA PEAU (ou les cheveux): Enlever immédiatement tous les vêtements contaminés. Rincer la peau à l'eau [ou se doucher].</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P304+P340</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>EN CAS D'INHALATION: transporter la personne à l'extérieur et la maintenir dans une position où elle peut confortablement respirer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P305+P351+P338</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>EN CAS DE CONTACT AVEC LES YEUX: Rincer avec précaution à l'eau pendant plusieurs minutes. Enlever les lentilles de contact si la victime en porte et si elles peuvent être facilement enlevées. Continuer à rincer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P308+P313</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>EN CAS d'exposition prouvée ou suspectée: consulter un médecin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>P312</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Appeler un CENTRE ANTIPOISON/un médecin/…/en cas de malaise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P321</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Traitement spécifique (voir … sur cette étiquette).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P332+P313</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>En cas d'irritation cutanée: consulter un médecin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P337+P313</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Si l'irritation oculaire persiste: consulter un médecin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P362+P364</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Enlever les vêtements contaminés et les laver avant réutilisation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P370+P378</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>En cas d'incendie: Utiliser… pour l'extinction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P403+P233</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Stocker dans un endroit bien ventilé. Maintenir le récipient fermé de manière étanche.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>P403+P235</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Stocker dans un endroit bien ventilé. Tenir au frais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P405</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Garder sous clef.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P501</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Éliminer le contenu/récipient dans …</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Mentions complémentaires</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
